--- a/data/trans_orig/P43C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Edad-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103425</t>
+          <t>106186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141379</t>
+          <t>141056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103425</t>
+          <t>106186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141379</t>
+          <t>141056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320484</t>
+          <t>320807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>358438</t>
+          <t>355677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320484</t>
+          <t>320807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>358438</t>
+          <t>355677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>364158</t>
+          <t>364502</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>411374</t>
+          <t>413265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>364158</t>
+          <t>364502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>411374</t>
+          <t>413265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208141</t>
+          <t>206250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>255357</t>
+          <t>255013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208141</t>
+          <t>206250</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>255357</t>
+          <t>255013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>466663</t>
+          <t>467211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>514168</t>
+          <t>516725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>466663</t>
+          <t>467211</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>514168</t>
+          <t>516725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172768</t>
+          <t>170211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>220273</t>
+          <t>219725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172768</t>
+          <t>170211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220273</t>
+          <t>219725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>346205</t>
+          <t>344386</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>385276</t>
+          <t>385357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>346205</t>
+          <t>344386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>385276</t>
+          <t>385357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121916</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160987</t>
+          <t>162806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121916</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160987</t>
+          <t>162806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>203004</t>
+          <t>204580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242805</t>
+          <t>243534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203004</t>
+          <t>204580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242805</t>
+          <t>243534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153035</t>
+          <t>152306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192836</t>
+          <t>191260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153035</t>
+          <t>152306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192836</t>
+          <t>191260</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,32%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113021</t>
+          <t>115570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147547</t>
+          <t>149587</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113021</t>
+          <t>115570</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147547</t>
+          <t>149587</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188126</t>
+          <t>186086</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222652</t>
+          <t>220103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188126</t>
+          <t>186086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222652</t>
+          <t>220103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50473</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79450</t>
+          <t>80696</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50473</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79450</t>
+          <t>80696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240581</t>
+          <t>239335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>269558</t>
+          <t>269491</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240581</t>
+          <t>239335</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269558</t>
+          <t>269491</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145887</t>
+          <t>146594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188882</t>
+          <t>188693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145887</t>
+          <t>146594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188882</t>
+          <t>188693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238432</t>
+          <t>238621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281427</t>
+          <t>280720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238432</t>
+          <t>238621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281427</t>
+          <t>280720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>428527</t>
+          <t>428657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>473668</t>
+          <t>473773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>428527</t>
+          <t>428657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>473668</t>
+          <t>473773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132129</t>
+          <t>132024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177270</t>
+          <t>177140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132129</t>
+          <t>132024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177270</t>
+          <t>177140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>550619</t>
+          <t>553129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>595476</t>
+          <t>596372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>550619</t>
+          <t>553129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>595476</t>
+          <t>596372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110367</t>
+          <t>109471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>155224</t>
+          <t>152714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110367</t>
+          <t>109471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155224</t>
+          <t>152714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>472169</t>
+          <t>468957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>513169</t>
+          <t>512849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>472169</t>
+          <t>468957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>513169</t>
+          <t>512849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103030</t>
+          <t>103350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>147242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103030</t>
+          <t>103350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>147242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>294813</t>
+          <t>296434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>335677</t>
+          <t>333458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>294813</t>
+          <t>296434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>335677</t>
+          <t>333458</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105127</t>
+          <t>107346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>144370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105127</t>
+          <t>107346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>144370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159511</t>
+          <t>162209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>198804</t>
+          <t>198343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159511</t>
+          <t>162209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198804</t>
+          <t>198343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150272</t>
+          <t>150733</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>189565</t>
+          <t>186867</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150272</t>
+          <t>150733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189565</t>
+          <t>186867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -4179,12 +4179,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>91953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129598</t>
+          <t>129061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>91953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129598</t>
+          <t>129061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247723</t>
+          <t>248260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>284762</t>
+          <t>285368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247723</t>
+          <t>248260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284762</t>
+          <t>285368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2233561</t>
+          <t>2233642</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2345963</t>
+          <t>2354668</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2233561</t>
+          <t>2233642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2345963</t>
+          <t>2354668</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1176390</t>
+          <t>1167685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1288792</t>
+          <t>1288711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1176390</t>
+          <t>1167685</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1288792</t>
+          <t>1288711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144373</t>
+          <t>145943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183076</t>
+          <t>183449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144373</t>
+          <t>145943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183076</t>
+          <t>183449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202643</t>
+          <t>202270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241346</t>
+          <t>239776</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202643</t>
+          <t>202270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241346</t>
+          <t>239776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>358801</t>
+          <t>354155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>401199</t>
+          <t>399673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>358801</t>
+          <t>354155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>401199</t>
+          <t>399673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160384</t>
+          <t>161910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202782</t>
+          <t>207428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160384</t>
+          <t>161910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>202782</t>
+          <t>207428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>498529</t>
+          <t>496393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>538421</t>
+          <t>536258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>498529</t>
+          <t>496393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>538421</t>
+          <t>536258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118660</t>
+          <t>120823</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158552</t>
+          <t>160688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118660</t>
+          <t>120823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158552</t>
+          <t>160688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>470218</t>
+          <t>469659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>515858</t>
+          <t>512643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>470218</t>
+          <t>469659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>515858</t>
+          <t>512643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127548</t>
+          <t>130763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173188</t>
+          <t>173747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127548</t>
+          <t>130763</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173188</t>
+          <t>173747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>309541</t>
+          <t>311211</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>353281</t>
+          <t>355169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309541</t>
+          <t>311211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>353281</t>
+          <t>355169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140438</t>
+          <t>138550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>184178</t>
+          <t>182508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140438</t>
+          <t>138550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184178</t>
+          <t>182508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>196563</t>
+          <t>197089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>234216</t>
+          <t>234981</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196563</t>
+          <t>197089</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234216</t>
+          <t>234981</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138474</t>
+          <t>137709</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176127</t>
+          <t>175601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138474</t>
+          <t>137709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176127</t>
+          <t>175601</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117551</t>
+          <t>119021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162205</t>
+          <t>163291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117551</t>
+          <t>119021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162205</t>
+          <t>163291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -6335,12 +6335,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230270</t>
+          <t>229184</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274924</t>
+          <t>273454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>230270</t>
+          <t>229184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274924</t>
+          <t>273454</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6495,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2183875</t>
+          <t>2178249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2297736</t>
+          <t>2294711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2183875</t>
+          <t>2178249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2297736</t>
+          <t>2294711</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1208936</t>
+          <t>1211961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1208936</t>
+          <t>1211961</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -6902,32 +6902,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>67664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6937,32 +6937,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>67664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -6980,32 +6980,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>220664</t>
+          <t>254377</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202996</t>
+          <t>234638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234920</t>
+          <t>268819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7015,32 +7015,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>220664</t>
+          <t>254377</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202996</t>
+          <t>234638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234920</t>
+          <t>268819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -7058,17 +7058,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7093,17 +7093,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7140,32 +7140,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205197</t>
+          <t>170079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>315760</t>
+          <t>213019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7175,32 +7175,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>191544</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205197</t>
+          <t>170079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>315760</t>
+          <t>213019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>57,87%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>150242</t>
+          <t>176581</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79405</t>
+          <t>155106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189968</t>
+          <t>198046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150242</t>
+          <t>176581</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79405</t>
+          <t>155106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189968</t>
+          <t>198046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -7296,17 +7296,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>395165</t>
+          <t>368125</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>395165</t>
+          <t>368125</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>395165</t>
+          <t>368125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7331,17 +7331,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>395165</t>
+          <t>368125</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>395165</t>
+          <t>368125</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>395165</t>
+          <t>368125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7378,32 +7378,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239703</t>
+          <t>272034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270023</t>
+          <t>305486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>289809</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>239703</t>
+          <t>272034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>270023</t>
+          <t>305486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -7456,32 +7456,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>113984</t>
+          <t>133527</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99843</t>
+          <t>117850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130163</t>
+          <t>151302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7491,32 +7491,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113984</t>
+          <t>133527</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99843</t>
+          <t>117850</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130163</t>
+          <t>151302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -7534,17 +7534,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>369866</t>
+          <t>423336</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>369866</t>
+          <t>423336</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>369866</t>
+          <t>423336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7569,17 +7569,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>369866</t>
+          <t>423336</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>369866</t>
+          <t>423336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>369866</t>
+          <t>423336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7616,32 +7616,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>388218</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>370778</t>
+          <t>366314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>411291</t>
+          <t>396163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7651,32 +7651,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>388218</t>
+          <t>380803</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>370778</t>
+          <t>366314</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>411291</t>
+          <t>396163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -7694,32 +7694,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>112466</t>
+          <t>126244</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89393</t>
+          <t>110884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129906</t>
+          <t>140733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7729,32 +7729,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>112466</t>
+          <t>126244</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89393</t>
+          <t>110884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129906</t>
+          <t>140733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -7772,17 +7772,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>500684</t>
+          <t>507047</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>500684</t>
+          <t>507047</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>500684</t>
+          <t>507047</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7807,17 +7807,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>500684</t>
+          <t>507047</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>500684</t>
+          <t>507047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>500684</t>
+          <t>507047</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7854,32 +7854,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>284328</t>
+          <t>314100</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>270551</t>
+          <t>299334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>298159</t>
+          <t>330013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7889,32 +7889,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>284328</t>
+          <t>314100</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>270551</t>
+          <t>299334</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298159</t>
+          <t>330013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -7932,32 +7932,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>115311</t>
+          <t>130601</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101480</t>
+          <t>114688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129088</t>
+          <t>145367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7967,32 +7967,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>115311</t>
+          <t>130601</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101480</t>
+          <t>114688</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129088</t>
+          <t>145367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8010,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>399639</t>
+          <t>444701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>399639</t>
+          <t>444701</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>399639</t>
+          <t>444701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>399639</t>
+          <t>444701</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>399639</t>
+          <t>444701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>399639</t>
+          <t>444701</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75403</t>
+          <t>202590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>331477</t>
+          <t>228787</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>197491</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75403</t>
+          <t>202590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>331477</t>
+          <t>228787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>323434</t>
+          <t>129589</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189448</t>
+          <t>116503</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>445522</t>
+          <t>142700</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>323434</t>
+          <t>129589</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>189448</t>
+          <t>116503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>445522</t>
+          <t>142700</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -8248,17 +8248,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>520925</t>
+          <t>345290</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>520925</t>
+          <t>345290</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>520925</t>
+          <t>345290</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>520925</t>
+          <t>345290</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>520925</t>
+          <t>345290</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>520925</t>
+          <t>345290</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8330,32 +8330,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>170713</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144059</t>
+          <t>154859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172165</t>
+          <t>184391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8365,32 +8365,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>170713</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144059</t>
+          <t>154859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172165</t>
+          <t>184391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -8408,32 +8408,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>200039</t>
+          <t>218368</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185139</t>
+          <t>204690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>213245</t>
+          <t>234222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8443,32 +8443,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>200039</t>
+          <t>218368</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>185139</t>
+          <t>204690</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>213245</t>
+          <t>234222</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -8486,17 +8486,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>357304</t>
+          <t>389081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357304</t>
+          <t>389081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>357304</t>
+          <t>389081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8521,17 +8521,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>357304</t>
+          <t>389081</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>357304</t>
+          <t>389081</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>357304</t>
+          <t>389081</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8568,32 +8568,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1180025</t>
+          <t>1564073</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1722853</t>
+          <t>1661715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8603,32 +8603,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1180025</t>
+          <t>1564073</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1722853</t>
+          <t>1661715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -8646,32 +8646,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1084575</t>
+          <t>1118167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1627403</t>
+          <t>1215809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8681,32 +8681,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1084575</t>
+          <t>1118167</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1627403</t>
+          <t>1215809</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8759,17 +8759,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
